--- a/AxisBank_Test_Cases.xlsx
+++ b/AxisBank_Test_Cases.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/13da4701092726d5/Testing/Axis Bank/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="821" documentId="11_DFBD7CE7ECB7CDE8F38D34988E10651BB7941D7F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F94D5E3-A54C-4184-BF51-E1A73C89FF2D}"/>
+  <xr:revisionPtr revIDLastSave="824" documentId="11_DFBD7CE7ECB7CDE8F38D34988E10651BB7941D7F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA09026D-BC2F-44C3-865F-8227960FA7C3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="29" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vesrion History" sheetId="1" r:id="rId1"/>
@@ -7142,12 +7142,14 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -7352,7 +7354,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -7453,27 +7455,6 @@
     <xf numFmtId="0" fontId="12" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7482,6 +7463,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7826,128 +7819,124 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.77734375" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" customWidth="1"/>
+    <col min="4" max="4" width="7.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="41" t="s">
         <v>215</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
     </row>
     <row r="2" spans="1:10" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="37" t="s">
         <v>216</v>
       </c>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="42" t="s">
         <v>2141</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="41"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="44"/>
     </row>
     <row r="3" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="37" t="s">
         <v>217</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="42" t="s">
         <v>2142</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="41"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="44"/>
     </row>
     <row r="4" spans="1:10" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="37" t="s">
         <v>218</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="42" t="s">
         <v>2143</v>
       </c>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="41"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="44"/>
     </row>
     <row r="5" spans="1:10" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="37" t="s">
         <v>219</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="42" t="s">
         <v>2144</v>
       </c>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="41"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="44"/>
     </row>
     <row r="6" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="37" t="s">
         <v>220</v>
       </c>
-      <c r="B6" s="43">
-        <v>45667</v>
-      </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
       <c r="J6" s="44"/>
     </row>
     <row r="7" spans="1:10" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="37" t="s">
         <v>221</v>
       </c>
-      <c r="B7" s="43">
-        <v>45708</v>
-      </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
       <c r="J7" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="B7:J7"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
     <mergeCell ref="B4:J4"/>
     <mergeCell ref="B5:J5"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B7:J7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8046,7 +8035,7 @@
       <c r="K3" s="17" t="s">
         <v>610</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -8082,7 +8071,7 @@
       <c r="K4" s="17" t="s">
         <v>616</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -8118,7 +8107,7 @@
       <c r="K5" s="17" t="s">
         <v>623</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -8154,7 +8143,7 @@
       <c r="K6" s="17" t="s">
         <v>629</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -8190,7 +8179,7 @@
       <c r="K7" s="17" t="s">
         <v>635</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
@@ -8226,7 +8215,7 @@
       <c r="K8" s="17" t="s">
         <v>641</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
     <row r="9" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
@@ -8262,7 +8251,7 @@
       <c r="K9" s="17" t="s">
         <v>360</v>
       </c>
-      <c r="L9" s="47"/>
+      <c r="L9" s="40"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -8375,7 +8364,7 @@
       <c r="K3" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -8411,7 +8400,7 @@
       <c r="K4" s="17" t="s">
         <v>426</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -8447,7 +8436,7 @@
       <c r="K5" s="17" t="s">
         <v>664</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -8483,7 +8472,7 @@
       <c r="K6" s="17" t="s">
         <v>670</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -8519,7 +8508,7 @@
       <c r="K7" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -8628,7 +8617,7 @@
       <c r="K3" s="12" t="s">
         <v>682</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
@@ -8664,7 +8653,7 @@
       <c r="K4" s="12" t="s">
         <v>688</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
@@ -8700,7 +8689,7 @@
       <c r="K5" s="12" t="s">
         <v>694</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
@@ -8736,7 +8725,7 @@
       <c r="K6" s="12" t="s">
         <v>700</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
@@ -8772,7 +8761,7 @@
       <c r="K7" s="12" t="s">
         <v>706</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
@@ -8808,7 +8797,7 @@
       <c r="K8" s="12" t="s">
         <v>713</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
     <row r="9" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
@@ -8844,7 +8833,7 @@
       <c r="K9" s="12" t="s">
         <v>720</v>
       </c>
-      <c r="L9" s="47"/>
+      <c r="L9" s="40"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -8955,7 +8944,7 @@
       <c r="K3" s="17" t="s">
         <v>726</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -8991,7 +8980,7 @@
       <c r="K4" s="17" t="s">
         <v>732</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -9027,7 +9016,7 @@
       <c r="K5" s="17" t="s">
         <v>738</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -9063,7 +9052,7 @@
       <c r="K6" s="17" t="s">
         <v>745</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -9099,7 +9088,7 @@
       <c r="K7" s="17" t="s">
         <v>751</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -9209,7 +9198,7 @@
       <c r="K3" s="17" t="s">
         <v>757</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -9245,7 +9234,7 @@
       <c r="K4" s="17" t="s">
         <v>764</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -9281,7 +9270,7 @@
       <c r="K5" s="17" t="s">
         <v>772</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -9317,7 +9306,7 @@
       <c r="K6" s="17" t="s">
         <v>778</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -9353,7 +9342,7 @@
       <c r="K7" s="17" t="s">
         <v>784</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
@@ -9389,7 +9378,7 @@
       <c r="K8" s="17" t="s">
         <v>790</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
     <row r="9" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
@@ -9425,7 +9414,7 @@
       <c r="K9" s="17" t="s">
         <v>796</v>
       </c>
-      <c r="L9" s="47"/>
+      <c r="L9" s="40"/>
     </row>
     <row r="10" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
@@ -9461,7 +9450,7 @@
       <c r="K10" s="17" t="s">
         <v>803</v>
       </c>
-      <c r="L10" s="47"/>
+      <c r="L10" s="40"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -9566,7 +9555,7 @@
       <c r="K3" s="17" t="s">
         <v>809</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -9602,7 +9591,7 @@
       <c r="K4" s="17" t="s">
         <v>815</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -9638,7 +9627,7 @@
       <c r="K5" s="17" t="s">
         <v>821</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -9674,7 +9663,7 @@
       <c r="K6" s="17" t="s">
         <v>827</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -9710,7 +9699,7 @@
       <c r="K7" s="17" t="s">
         <v>833</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
@@ -9746,7 +9735,7 @@
       <c r="K8" s="17" t="s">
         <v>841</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
     <row r="9" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
@@ -9782,7 +9771,7 @@
       <c r="K9" s="17" t="s">
         <v>847</v>
       </c>
-      <c r="L9" s="47"/>
+      <c r="L9" s="40"/>
     </row>
     <row r="10" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
@@ -9818,7 +9807,7 @@
       <c r="K10" s="17" t="s">
         <v>853</v>
       </c>
-      <c r="L10" s="47"/>
+      <c r="L10" s="40"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -9928,7 +9917,7 @@
       <c r="K3" s="12" t="s">
         <v>858</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
@@ -9964,7 +9953,7 @@
       <c r="K4" s="12" t="s">
         <v>864</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
@@ -10000,7 +9989,7 @@
       <c r="K5" s="12" t="s">
         <v>870</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
@@ -10036,7 +10025,7 @@
       <c r="K6" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
@@ -10072,7 +10061,7 @@
       <c r="K7" s="12" t="s">
         <v>881</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
@@ -10108,7 +10097,7 @@
       <c r="K8" s="12" t="s">
         <v>887</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -10218,7 +10207,7 @@
       <c r="K3" s="17" t="s">
         <v>893</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -10254,7 +10243,7 @@
       <c r="K4" s="17" t="s">
         <v>899</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -10290,7 +10279,7 @@
       <c r="K5" s="17" t="s">
         <v>906</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -10326,7 +10315,7 @@
       <c r="K6" s="17" t="s">
         <v>912</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -10362,7 +10351,7 @@
       <c r="K7" s="17" t="s">
         <v>918</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
@@ -10398,7 +10387,7 @@
       <c r="K8" s="17" t="s">
         <v>924</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
     <row r="9" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
@@ -10434,7 +10423,7 @@
       <c r="K9" s="17" t="s">
         <v>930</v>
       </c>
-      <c r="L9" s="47"/>
+      <c r="L9" s="40"/>
     </row>
     <row r="10" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
@@ -10470,7 +10459,7 @@
       <c r="K10" s="17" t="s">
         <v>936</v>
       </c>
-      <c r="L10" s="47"/>
+      <c r="L10" s="40"/>
     </row>
     <row r="11" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
@@ -10506,7 +10495,7 @@
       <c r="K11" s="17" t="s">
         <v>2123</v>
       </c>
-      <c r="L11" s="47"/>
+      <c r="L11" s="40"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -10618,7 +10607,7 @@
       <c r="K3" s="17" t="s">
         <v>942</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -10654,7 +10643,7 @@
       <c r="K4" s="17" t="s">
         <v>426</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -10690,7 +10679,7 @@
       <c r="K5" s="17" t="s">
         <v>664</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -10726,7 +10715,7 @@
       <c r="K6" s="17" t="s">
         <v>959</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -10762,7 +10751,7 @@
       <c r="K7" s="17" t="s">
         <v>965</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
@@ -10798,7 +10787,7 @@
       <c r="K8" s="17" t="s">
         <v>971</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -10904,7 +10893,7 @@
       <c r="K3" s="17" t="s">
         <v>977</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -10940,7 +10929,7 @@
       <c r="K4" s="17" t="s">
         <v>983</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -10976,7 +10965,7 @@
       <c r="K5" s="17" t="s">
         <v>990</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -11012,7 +11001,7 @@
       <c r="K6" s="17" t="s">
         <v>996</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -11048,7 +11037,7 @@
       <c r="K7" s="17" t="s">
         <v>1003</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
@@ -11084,7 +11073,7 @@
       <c r="K8" s="17" t="s">
         <v>1009</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
     <row r="9" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
@@ -11120,7 +11109,7 @@
       <c r="K9" s="17" t="s">
         <v>2124</v>
       </c>
-      <c r="L9" s="47"/>
+      <c r="L9" s="40"/>
     </row>
     <row r="10" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
@@ -11156,7 +11145,7 @@
       <c r="K10" s="17" t="s">
         <v>1016</v>
       </c>
-      <c r="L10" s="47"/>
+      <c r="L10" s="40"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -12081,7 +12070,7 @@
       <c r="K3" s="17" t="s">
         <v>1022</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -12117,7 +12106,7 @@
       <c r="K4" s="17" t="s">
         <v>1028</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -12153,7 +12142,7 @@
       <c r="K5" s="17" t="s">
         <v>1034</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -12189,7 +12178,7 @@
       <c r="K6" s="17" t="s">
         <v>360</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -12225,7 +12214,7 @@
       <c r="K7" s="17" t="s">
         <v>1045</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
@@ -12261,7 +12250,7 @@
       <c r="K8" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -12369,7 +12358,7 @@
       <c r="K3" s="17" t="s">
         <v>581</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -12405,7 +12394,7 @@
       <c r="K4" s="17" t="s">
         <v>1062</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -12441,7 +12430,7 @@
       <c r="K5" s="17" t="s">
         <v>1068</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -12477,7 +12466,7 @@
       <c r="K6" s="17" t="s">
         <v>1074</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -12513,7 +12502,7 @@
       <c r="K7" s="17" t="s">
         <v>1080</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -12624,7 +12613,7 @@
       <c r="K3" s="17" t="s">
         <v>1086</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -12660,7 +12649,7 @@
       <c r="K4" s="17" t="s">
         <v>1092</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -12696,7 +12685,7 @@
       <c r="K5" s="17" t="s">
         <v>1098</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -12732,7 +12721,7 @@
       <c r="K6" s="17" t="s">
         <v>1104</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -12768,7 +12757,7 @@
       <c r="K7" s="17" t="s">
         <v>1110</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -12876,7 +12865,7 @@
       <c r="K3" s="17" t="s">
         <v>1116</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -12912,7 +12901,7 @@
       <c r="K4" s="17" t="s">
         <v>1122</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -12948,7 +12937,7 @@
       <c r="K5" s="17" t="s">
         <v>1128</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -12984,7 +12973,7 @@
       <c r="K6" s="17" t="s">
         <v>1135</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -13020,7 +13009,7 @@
       <c r="K7" s="17" t="s">
         <v>1141</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
@@ -13056,7 +13045,7 @@
       <c r="K8" s="17" t="s">
         <v>1009</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
     <row r="9" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
@@ -13092,7 +13081,7 @@
       <c r="K9" s="17" t="s">
         <v>2124</v>
       </c>
-      <c r="L9" s="47"/>
+      <c r="L9" s="40"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -13203,7 +13192,7 @@
       <c r="K3" s="17" t="s">
         <v>1116</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -13239,7 +13228,7 @@
       <c r="K4" s="17" t="s">
         <v>1122</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -13275,7 +13264,7 @@
       <c r="K5" s="17" t="s">
         <v>1162</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -13311,7 +13300,7 @@
       <c r="K6" s="17" t="s">
         <v>1169</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -13347,7 +13336,7 @@
       <c r="K7" s="17" t="s">
         <v>1176</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
@@ -13383,7 +13372,7 @@
       <c r="K8" s="17" t="s">
         <v>1009</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
     <row r="9" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
@@ -13419,7 +13408,7 @@
       <c r="K9" s="17" t="s">
         <v>2124</v>
       </c>
-      <c r="L9" s="47"/>
+      <c r="L9" s="40"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -13528,7 +13517,7 @@
       <c r="K3" s="17" t="s">
         <v>1187</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -13564,7 +13553,7 @@
       <c r="K4" s="17" t="s">
         <v>1193</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -13600,7 +13589,7 @@
       <c r="K5" s="17" t="s">
         <v>1199</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -13636,7 +13625,7 @@
       <c r="K6" s="17" t="s">
         <v>1205</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -13672,7 +13661,7 @@
       <c r="K7" s="17" t="s">
         <v>803</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
@@ -13708,7 +13697,7 @@
       <c r="K8" s="17" t="s">
         <v>1217</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -13813,7 +13802,7 @@
       <c r="K3" s="17" t="s">
         <v>1223</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -13849,7 +13838,7 @@
       <c r="K4" s="17" t="s">
         <v>1229</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -13885,7 +13874,7 @@
       <c r="K5" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -13921,7 +13910,7 @@
       <c r="K6" s="17" t="s">
         <v>360</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -13957,7 +13946,7 @@
       <c r="K7" s="17" t="s">
         <v>1045</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
@@ -13993,7 +13982,7 @@
       <c r="K8" s="17" t="s">
         <v>510</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -14101,7 +14090,7 @@
       <c r="K3" s="17" t="s">
         <v>1255</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -14137,7 +14126,7 @@
       <c r="K4" s="17" t="s">
         <v>426</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -14173,7 +14162,7 @@
       <c r="K5" s="17" t="s">
         <v>1266</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -14209,7 +14198,7 @@
       <c r="K6" s="17" t="s">
         <v>360</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -14245,7 +14234,7 @@
       <c r="K7" s="17" t="s">
         <v>510</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
@@ -14281,7 +14270,7 @@
       <c r="K8" s="17" t="s">
         <v>516</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -14389,7 +14378,7 @@
       <c r="K3" s="17" t="s">
         <v>1287</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -14425,7 +14414,7 @@
       <c r="K4" s="17" t="s">
         <v>1287</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -14461,7 +14450,7 @@
       <c r="K5" s="17" t="s">
         <v>426</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -14497,7 +14486,7 @@
       <c r="K6" s="17" t="s">
         <v>682</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -14533,7 +14522,7 @@
       <c r="K7" s="17" t="s">
         <v>1308</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
@@ -14569,7 +14558,7 @@
       <c r="K8" s="17" t="s">
         <v>360</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -14679,7 +14668,7 @@
       <c r="K3" s="17" t="s">
         <v>1319</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -14715,7 +14704,7 @@
       <c r="K4" s="17" t="s">
         <v>1325</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -14751,7 +14740,7 @@
       <c r="K5" s="17" t="s">
         <v>1331</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -14787,7 +14776,7 @@
       <c r="K6" s="17" t="s">
         <v>713</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -14823,7 +14812,7 @@
       <c r="K7" s="17" t="s">
         <v>1141</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
@@ -14859,7 +14848,7 @@
       <c r="K8" s="17" t="s">
         <v>1176</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
     <row r="9" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
@@ -14895,7 +14884,7 @@
       <c r="K9" s="17" t="s">
         <v>1354</v>
       </c>
-      <c r="L9" s="47"/>
+      <c r="L9" s="40"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -14930,40 +14919,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="45" t="s">
+      <c r="D1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="45" t="s">
+      <c r="E1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="45" t="s">
+      <c r="G1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="45" t="s">
+      <c r="H1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="45" t="s">
+      <c r="I1" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="J1" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="45" t="s">
+      <c r="K1" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="45" t="s">
+      <c r="L1" s="38" t="s">
         <v>2145</v>
       </c>
     </row>
@@ -16147,7 +16136,7 @@
       <c r="K3" s="17" t="s">
         <v>1361</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -16183,7 +16172,7 @@
       <c r="K4" s="17" t="s">
         <v>1368</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -16219,7 +16208,7 @@
       <c r="K5" s="17" t="s">
         <v>1374</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -16255,7 +16244,7 @@
       <c r="K6" s="17" t="s">
         <v>1380</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -16291,7 +16280,7 @@
       <c r="K7" s="17" t="s">
         <v>1386</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
@@ -16327,7 +16316,7 @@
       <c r="K8" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -16434,7 +16423,7 @@
       <c r="K3" s="17" t="s">
         <v>1223</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -16470,7 +16459,7 @@
       <c r="K4" s="17" t="s">
         <v>1229</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -16506,7 +16495,7 @@
       <c r="K5" s="17" t="s">
         <v>1403</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -16542,7 +16531,7 @@
       <c r="K6" s="17" t="s">
         <v>360</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -16578,7 +16567,7 @@
       <c r="K7" s="17" t="s">
         <v>1045</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
@@ -16614,7 +16603,7 @@
       <c r="K8" s="17" t="s">
         <v>1416</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -16723,7 +16712,7 @@
       <c r="K3" s="17" t="s">
         <v>581</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -16759,7 +16748,7 @@
       <c r="K4" s="17" t="s">
         <v>1427</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -16795,7 +16784,7 @@
       <c r="K5" s="17" t="s">
         <v>1068</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -16831,7 +16820,7 @@
       <c r="K6" s="17" t="s">
         <v>664</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -16867,7 +16856,7 @@
       <c r="K7" s="17" t="s">
         <v>1080</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
@@ -16903,7 +16892,7 @@
       <c r="K8" s="17" t="s">
         <v>1448</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -19080,7 +19069,7 @@
       <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="45" t="s">
+      <c r="L1" s="38" t="s">
         <v>2145</v>
       </c>
     </row>
@@ -22224,7 +22213,7 @@
       <c r="K3" s="17" t="s">
         <v>367</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -22260,7 +22249,7 @@
       <c r="K4" s="17" t="s">
         <v>373</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -22296,7 +22285,7 @@
       <c r="K5" s="17" t="s">
         <v>379</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -22332,7 +22321,7 @@
       <c r="K6" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -22368,7 +22357,7 @@
       <c r="K7" s="17" t="s">
         <v>395</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
@@ -22404,7 +22393,7 @@
       <c r="K8" s="17" t="s">
         <v>401</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
     <row r="9" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
@@ -22440,7 +22429,7 @@
       <c r="K9" s="17" t="s">
         <v>407</v>
       </c>
-      <c r="L9" s="47"/>
+      <c r="L9" s="40"/>
     </row>
     <row r="10" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
@@ -22476,7 +22465,7 @@
       <c r="K10" s="17" t="s">
         <v>413</v>
       </c>
-      <c r="L10" s="47"/>
+      <c r="L10" s="40"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -22944,7 +22933,7 @@
       <c r="K3" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -22980,7 +22969,7 @@
       <c r="K4" s="17" t="s">
         <v>426</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -23016,7 +23005,7 @@
       <c r="K5" s="17" t="s">
         <v>432</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -23052,7 +23041,7 @@
       <c r="K6" s="17" t="s">
         <v>438</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -23088,7 +23077,7 @@
       <c r="K7" s="17" t="s">
         <v>444</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
@@ -23124,7 +23113,7 @@
       <c r="K8" s="17" t="s">
         <v>450</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
     <row r="9" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
@@ -23160,7 +23149,7 @@
       <c r="K9" s="17" t="s">
         <v>456</v>
       </c>
-      <c r="L9" s="47"/>
+      <c r="L9" s="40"/>
     </row>
     <row r="10" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
@@ -23196,7 +23185,7 @@
       <c r="K10" s="17" t="s">
         <v>463</v>
       </c>
-      <c r="L10" s="47"/>
+      <c r="L10" s="40"/>
     </row>
     <row r="11" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
@@ -23232,7 +23221,7 @@
       <c r="K11" s="17" t="s">
         <v>2112</v>
       </c>
-      <c r="L11" s="47"/>
+      <c r="L11" s="40"/>
     </row>
     <row r="12" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -23268,7 +23257,7 @@
       <c r="K12" s="17" t="s">
         <v>469</v>
       </c>
-      <c r="L12" s="47"/>
+      <c r="L12" s="40"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -23384,7 +23373,7 @@
       <c r="K3" s="17" t="s">
         <v>475</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -23420,7 +23409,7 @@
       <c r="K4" s="17" t="s">
         <v>481</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -23456,7 +23445,7 @@
       <c r="K5" s="17" t="s">
         <v>487</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -23492,7 +23481,7 @@
       <c r="K6" s="17" t="s">
         <v>493</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -23528,7 +23517,7 @@
       <c r="K7" s="17" t="s">
         <v>499</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
@@ -23564,7 +23553,7 @@
       <c r="K8" s="17" t="s">
         <v>360</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
     <row r="9" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
@@ -23600,7 +23589,7 @@
       <c r="K9" s="17" t="s">
         <v>510</v>
       </c>
-      <c r="L9" s="47"/>
+      <c r="L9" s="40"/>
     </row>
     <row r="10" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
@@ -23636,7 +23625,7 @@
       <c r="K10" s="17" t="s">
         <v>516</v>
       </c>
-      <c r="L10" s="47"/>
+      <c r="L10" s="40"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -23749,7 +23738,7 @@
       <c r="K3" s="17" t="s">
         <v>522</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -23785,7 +23774,7 @@
       <c r="K4" s="17" t="s">
         <v>528</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -23821,7 +23810,7 @@
       <c r="K5" s="17" t="s">
         <v>487</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -23857,7 +23846,7 @@
       <c r="K6" s="17" t="s">
         <v>539</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -23893,7 +23882,7 @@
       <c r="K7" s="17" t="s">
         <v>547</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
@@ -23929,7 +23918,7 @@
       <c r="K8" s="17" t="s">
         <v>554</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
     <row r="9" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
@@ -23965,7 +23954,7 @@
       <c r="K9" s="17" t="s">
         <v>561</v>
       </c>
-      <c r="L9" s="47"/>
+      <c r="L9" s="40"/>
     </row>
     <row r="10" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
@@ -24001,7 +23990,7 @@
       <c r="K10" s="17" t="s">
         <v>569</v>
       </c>
-      <c r="L10" s="47"/>
+      <c r="L10" s="40"/>
     </row>
     <row r="11" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
@@ -24037,7 +24026,7 @@
       <c r="K11" s="17" t="s">
         <v>1217</v>
       </c>
-      <c r="L11" s="47"/>
+      <c r="L11" s="40"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -24147,7 +24136,7 @@
       <c r="K3" s="17" t="s">
         <v>575</v>
       </c>
-      <c r="L3" s="46"/>
+      <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -24183,7 +24172,7 @@
       <c r="K4" s="17" t="s">
         <v>581</v>
       </c>
-      <c r="L4" s="47"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
@@ -24219,7 +24208,7 @@
       <c r="K5" s="17" t="s">
         <v>587</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -24255,7 +24244,7 @@
       <c r="K6" s="17" t="s">
         <v>360</v>
       </c>
-      <c r="L6" s="47"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
@@ -24291,7 +24280,7 @@
       <c r="K7" s="17" t="s">
         <v>598</v>
       </c>
-      <c r="L7" s="47"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
@@ -24327,7 +24316,7 @@
       <c r="K8" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="40"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
